--- a/eod_logger_4/Uganda_2023/Recordings_Sessions_Metadata.xlsx
+++ b/eod_logger_4/Uganda_2023/Recordings_Sessions_Metadata.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\stefa\Seafile\Uni\01 Research Projects\04 Uganda 2023 EOD loggers\01 Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Projects\EOD_pulse_analysis\eod_logger_4\Uganda_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0853D337-EE2B-4439-B7EE-57F12B160063}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A1D4A2-6603-4022-97FE-4A3E0643B036}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14400" yWindow="0" windowWidth="24096" windowHeight="20976" xr2:uid="{1B50041A-606E-4BAA-8BC2-5A1CB87C2F31}"/>
+    <workbookView xWindow="14400" yWindow="0" windowWidth="24090" windowHeight="20970" xr2:uid="{1B50041A-606E-4BAA-8BC2-5A1CB87C2F31}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -539,7 +539,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -555,7 +555,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -852,17 +852,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B4DF18-2126-4684-B12F-60ED5D48E1F2}">
   <dimension ref="A1:BE73"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="47" width="8.77734375" style="4"/>
-    <col min="48" max="49" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="47" width="8.7109375" style="4"/>
+    <col min="48" max="49" width="18.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1035,7 +1036,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -1046,7 +1047,7 @@
         <v>45210</v>
       </c>
       <c r="D2" s="2">
-        <v>45182</v>
+        <v>45212</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>47</v>
@@ -1106,7 +1107,7 @@
       </c>
       <c r="BE2" s="1"/>
     </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -1117,7 +1118,7 @@
         <v>45210</v>
       </c>
       <c r="D3" s="2">
-        <v>45182</v>
+        <v>45212</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>49</v>
@@ -1177,7 +1178,7 @@
       </c>
       <c r="BE3" s="1"/>
     </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
@@ -1248,7 +1249,7 @@
       </c>
       <c r="BE4" s="1"/>
     </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
@@ -1313,7 +1314,7 @@
       </c>
       <c r="BE5" s="1"/>
     </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -1382,7 +1383,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -1456,7 +1457,7 @@
       </c>
       <c r="BE7" s="1"/>
     </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
@@ -1547,7 +1548,7 @@
       </c>
       <c r="BE8" s="1"/>
     </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
@@ -1637,7 +1638,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
@@ -1725,7 +1726,7 @@
       </c>
       <c r="BE10" s="1"/>
     </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
@@ -1812,7 +1813,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -1893,7 +1894,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -1968,7 +1969,7 @@
       </c>
       <c r="BE13" s="1"/>
     </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
@@ -2037,7 +2038,7 @@
       </c>
       <c r="BE14" s="1"/>
     </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>34</v>
       </c>
@@ -2119,7 +2120,7 @@
       </c>
       <c r="BE15" s="1"/>
     </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>34</v>
       </c>
@@ -2188,7 +2189,7 @@
       </c>
       <c r="BE16" s="1"/>
     </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -2253,7 +2254,7 @@
       </c>
       <c r="BE17" s="1"/>
     </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -2318,7 +2319,7 @@
       </c>
       <c r="BE18" s="1"/>
     </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -2329,7 +2330,7 @@
         <v>45208</v>
       </c>
       <c r="D19" s="2">
-        <v>45180</v>
+        <v>45210</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>53</v>
@@ -2387,7 +2388,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -2450,7 +2451,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
@@ -2511,7 +2512,7 @@
       </c>
       <c r="BE21" s="1"/>
     </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -2574,7 +2575,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
@@ -2635,7 +2636,7 @@
       </c>
       <c r="BE23" s="1"/>
     </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -2698,7 +2699,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -2761,7 +2762,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>23</v>
       </c>
@@ -2824,7 +2825,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>23</v>
       </c>
@@ -2896,7 +2897,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2959,7 +2960,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3022,7 +3023,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>23</v>
       </c>
@@ -3083,7 +3084,7 @@
       </c>
       <c r="BE30" s="1"/>
     </row>
-    <row r="31" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>23</v>
       </c>
@@ -3144,7 +3145,7 @@
       </c>
       <c r="BE31" s="1"/>
     </row>
-    <row r="32" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>23</v>
       </c>
@@ -3205,7 +3206,7 @@
       </c>
       <c r="BE32" s="1"/>
     </row>
-    <row r="33" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>23</v>
       </c>
@@ -3268,7 +3269,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>23</v>
       </c>
@@ -3329,7 +3330,7 @@
       </c>
       <c r="BE34" s="1"/>
     </row>
-    <row r="35" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>23</v>
       </c>
@@ -3393,7 +3394,7 @@
       </c>
       <c r="BE35" s="1"/>
     </row>
-    <row r="36" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>23</v>
       </c>
@@ -3454,7 +3455,7 @@
       </c>
       <c r="BE36" s="1"/>
     </row>
-    <row r="37" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>23</v>
       </c>
@@ -3515,7 +3516,7 @@
       </c>
       <c r="BE37" s="1"/>
     </row>
-    <row r="38" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>23</v>
       </c>
@@ -3576,7 +3577,7 @@
       </c>
       <c r="BE38" s="1"/>
     </row>
-    <row r="39" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>12</v>
       </c>
@@ -3640,7 +3641,7 @@
       </c>
       <c r="BE39" s="1"/>
     </row>
-    <row r="40" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>12</v>
       </c>
@@ -3704,7 +3705,7 @@
       </c>
       <c r="BE40" s="1"/>
     </row>
-    <row r="41" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>12</v>
       </c>
@@ -3768,7 +3769,7 @@
       </c>
       <c r="BE41" s="1"/>
     </row>
-    <row r="42" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>12</v>
       </c>
@@ -3832,7 +3833,7 @@
       </c>
       <c r="BE42" s="1"/>
     </row>
-    <row r="43" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>12</v>
       </c>
@@ -3896,7 +3897,7 @@
       </c>
       <c r="BE43" s="1"/>
     </row>
-    <row r="44" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>12</v>
       </c>
@@ -3962,7 +3963,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>12</v>
       </c>
@@ -4026,7 +4027,7 @@
       </c>
       <c r="BE45" s="1"/>
     </row>
-    <row r="46" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>12</v>
       </c>
@@ -4092,7 +4093,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>12</v>
       </c>
@@ -4158,7 +4159,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>12</v>
       </c>
@@ -4224,7 +4225,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>12</v>
       </c>
@@ -4290,7 +4291,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>12</v>
       </c>
@@ -4354,7 +4355,7 @@
       </c>
       <c r="BE50" s="1"/>
     </row>
-    <row r="51" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>12</v>
       </c>
@@ -4418,7 +4419,7 @@
       </c>
       <c r="BE51" s="1"/>
     </row>
-    <row r="52" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>12</v>
       </c>
@@ -4479,7 +4480,7 @@
       </c>
       <c r="BE52" s="1"/>
     </row>
-    <row r="53" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>12</v>
       </c>
@@ -4542,7 +4543,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>12</v>
       </c>
@@ -4603,7 +4604,7 @@
       </c>
       <c r="BE54" s="1"/>
     </row>
-    <row r="55" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>12</v>
       </c>
@@ -4664,7 +4665,7 @@
       </c>
       <c r="BE55" s="1"/>
     </row>
-    <row r="56" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>12</v>
       </c>
@@ -4725,7 +4726,7 @@
       </c>
       <c r="BE56" s="1"/>
     </row>
-    <row r="57" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>12</v>
       </c>
@@ -4786,7 +4787,7 @@
       </c>
       <c r="BE57" s="1"/>
     </row>
-    <row r="58" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>12</v>
       </c>
@@ -4847,7 +4848,7 @@
       </c>
       <c r="BE58" s="1"/>
     </row>
-    <row r="59" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>15</v>
       </c>
@@ -4858,7 +4859,7 @@
         <v>45210</v>
       </c>
       <c r="D59" s="2">
-        <v>45182</v>
+        <v>45212</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>14</v>
@@ -4918,7 +4919,7 @@
       </c>
       <c r="BE59" s="1"/>
     </row>
-    <row r="60" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>15</v>
       </c>
@@ -4929,7 +4930,7 @@
         <v>45210</v>
       </c>
       <c r="D60" s="2">
-        <v>45182</v>
+        <v>45212</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>37</v>
@@ -4991,7 +4992,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>15</v>
       </c>
@@ -5055,7 +5056,7 @@
       </c>
       <c r="BE61" s="4"/>
     </row>
-    <row r="62" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>15</v>
       </c>
@@ -5119,7 +5120,7 @@
       </c>
       <c r="BE62" s="4"/>
     </row>
-    <row r="63" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>15</v>
       </c>
@@ -5183,7 +5184,7 @@
       </c>
       <c r="BE63" s="1"/>
     </row>
-    <row r="64" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>15</v>
       </c>
@@ -5247,7 +5248,7 @@
       </c>
       <c r="BE64" s="1"/>
     </row>
-    <row r="65" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>15</v>
       </c>
@@ -5311,7 +5312,7 @@
       </c>
       <c r="BE65" s="1"/>
     </row>
-    <row r="66" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>15</v>
       </c>
@@ -5353,7 +5354,7 @@
         <v>45232.793437499997</v>
       </c>
       <c r="AX66" s="1">
-        <f t="shared" ref="AX66:AX97" si="2">(AW66-AV66)*24</f>
+        <f t="shared" ref="AX66:AX73" si="2">(AW66-AV66)*24</f>
         <v>30.333611111040227</v>
       </c>
       <c r="AY66" s="1">
@@ -5376,7 +5377,7 @@
       </c>
       <c r="BE66" s="1"/>
     </row>
-    <row r="67" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>15</v>
       </c>
@@ -5440,7 +5441,7 @@
       </c>
       <c r="BE67" s="1"/>
     </row>
-    <row r="68" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>15</v>
       </c>
@@ -5504,7 +5505,7 @@
       </c>
       <c r="BE68" s="1"/>
     </row>
-    <row r="69" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>15</v>
       </c>
@@ -5570,7 +5571,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="70" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>15</v>
       </c>
@@ -5634,7 +5635,7 @@
       </c>
       <c r="BE70" s="1"/>
     </row>
-    <row r="71" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>15</v>
       </c>
@@ -5700,7 +5701,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>15</v>
       </c>
@@ -5764,7 +5765,7 @@
       </c>
       <c r="BE72" s="1"/>
     </row>
-    <row r="73" spans="1:57" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>15</v>
       </c>

--- a/eod_logger_4/Uganda_2023/Recordings_Sessions_Metadata.xlsx
+++ b/eod_logger_4/Uganda_2023/Recordings_Sessions_Metadata.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Projects\EOD_pulse_analysis\eod_logger_4\Uganda_2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66A1D4A2-6603-4022-97FE-4A3E0643B036}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67BD2878-F70A-4D5D-8730-53AB5F182036}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14400" yWindow="0" windowWidth="24090" windowHeight="20970" xr2:uid="{1B50041A-606E-4BAA-8BC2-5A1CB87C2F31}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="787" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="754" uniqueCount="113">
   <si>
     <t>System</t>
   </si>
@@ -345,9 +345,6 @@
     <t>Dominant_veg</t>
   </si>
   <si>
-    <t>Moon_phase</t>
-  </si>
-  <si>
     <t>Weather</t>
   </si>
   <si>
@@ -357,66 +354,6 @@
     <t>Papyrus</t>
   </si>
   <si>
-    <t>Depth_ch0_set_cm</t>
-  </si>
-  <si>
-    <t>Depth_mid_set_cm</t>
-  </si>
-  <si>
-    <t>Depth_ch7_set_cm</t>
-  </si>
-  <si>
-    <t>DO_ch0_set_AS</t>
-  </si>
-  <si>
-    <t>DO_mid_set_AS</t>
-  </si>
-  <si>
-    <t>DO_ch7_set_AS</t>
-  </si>
-  <si>
-    <t>T_ch0_set_C</t>
-  </si>
-  <si>
-    <t>T_mid_set_C</t>
-  </si>
-  <si>
-    <t>T_ch7_set_C</t>
-  </si>
-  <si>
-    <t>Turbidity_set_NTU</t>
-  </si>
-  <si>
-    <t>Depth_ch0_retr_cm</t>
-  </si>
-  <si>
-    <t>Depth_mid_retr_cm</t>
-  </si>
-  <si>
-    <t>Depth_ch7_retr_cm</t>
-  </si>
-  <si>
-    <t>DO_ch0_retr_AS</t>
-  </si>
-  <si>
-    <t>DO_mid_retr_AS</t>
-  </si>
-  <si>
-    <t>DO_ch7_retr_AS</t>
-  </si>
-  <si>
-    <t>T_ch0_retr_C</t>
-  </si>
-  <si>
-    <t>T_mid_retr_C</t>
-  </si>
-  <si>
-    <t>T_ch7_retr_C</t>
-  </si>
-  <si>
-    <t>Turbidity_retr_NTU</t>
-  </si>
-  <si>
     <t>Papyrus, Grass</t>
   </si>
   <si>
@@ -430,42 +367,6 @@
   </si>
   <si>
     <t>water lillies, heavy rain</t>
-  </si>
-  <si>
-    <t>pH_ch0_set</t>
-  </si>
-  <si>
-    <t>pH_mid_set</t>
-  </si>
-  <si>
-    <t>pH_ch7_set</t>
-  </si>
-  <si>
-    <t>Conductivity_ch0_set_uS</t>
-  </si>
-  <si>
-    <t>Conductivity_mid_set_uS</t>
-  </si>
-  <si>
-    <t>Conductivity_ch7_set_uS</t>
-  </si>
-  <si>
-    <t>pH_ch0_retr</t>
-  </si>
-  <si>
-    <t>pH_mid_retr</t>
-  </si>
-  <si>
-    <t>pH_ch7_retr</t>
-  </si>
-  <si>
-    <t>Conductivity_ch0_retr_uS</t>
-  </si>
-  <si>
-    <t>Conductivity_mid_retr_uS</t>
-  </si>
-  <si>
-    <t>Conductivity_ch7_retr_uS</t>
   </si>
 </sst>
 </file>
@@ -851,7 +752,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B2B4DF18-2126-4684-B12F-60ED5D48E1F2}">
-  <dimension ref="A1:BE73"/>
+  <dimension ref="A1:X73"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -859,11 +760,12 @@
     <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="10" max="47" width="8.7109375" style="4"/>
-    <col min="48" max="49" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="8.7109375" style="4"/>
+    <col min="15" max="15" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -901,142 +803,43 @@
         <v>104</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="N1" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="R1" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="U1" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="V1" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="W1" s="4" t="s">
-        <v>135</v>
-      </c>
-      <c r="X1" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="Z1" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="AA1" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="AB1" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="AC1" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="AD1" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="AE1" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="AF1" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="AG1" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="AH1" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="AI1" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="AJ1" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="AK1" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="AL1" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="AM1" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="AN1" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="AO1" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="AP1" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="AQ1" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="AR1" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="AS1" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="AT1" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="AU1" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="AV1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="AW1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="AX1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="AY1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="AZ1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="BA1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="BB1" s="1" t="s">
+      <c r="U1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="BC1" s="10" t="s">
+      <c r="V1" s="10" t="s">
         <v>85</v>
       </c>
-      <c r="BD1" s="10" t="s">
+      <c r="W1" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="BE1" s="1" t="s">
+      <c r="X1" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -1071,43 +874,42 @@
         <v>2</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="N2" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="AU2"/>
-      <c r="AV2" s="3">
+        <v>109</v>
+      </c>
+      <c r="O2" s="3">
         <v>45210.385462962964</v>
       </c>
-      <c r="AW2" s="3">
+      <c r="P2" s="3">
         <v>45211.753541666665</v>
       </c>
-      <c r="AX2" s="1">
-        <f t="shared" ref="AX2:AX33" si="0">(AW2-AV2)*24</f>
+      <c r="Q2" s="1">
+        <f t="shared" ref="Q2:Q33" si="0">(P2-O2)*24</f>
         <v>32.833888888824731</v>
       </c>
-      <c r="AY2" s="1">
+      <c r="R2" s="1">
         <v>10</v>
       </c>
-      <c r="AZ2" s="4">
+      <c r="S2" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA2" s="4">
+      <c r="T2" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB2" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC2" s="9">
+      <c r="U2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V2" s="9">
         <v>374592</v>
       </c>
-      <c r="BD2" s="9">
+      <c r="W2" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE2" s="1"/>
-    </row>
-    <row r="3" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X2" s="1"/>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
@@ -1142,43 +944,42 @@
         <v>7</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="AU3"/>
-      <c r="AV3" s="3">
+        <v>109</v>
+      </c>
+      <c r="O3" s="3">
         <v>45210.4062962963</v>
       </c>
-      <c r="AW3" s="3">
+      <c r="P3" s="3">
         <v>45211.704884259256</v>
       </c>
-      <c r="AX3" s="1">
+      <c r="Q3" s="1">
         <f t="shared" si="0"/>
         <v>31.166111110942438</v>
       </c>
-      <c r="AY3" s="1">
+      <c r="R3" s="1">
         <v>10</v>
       </c>
-      <c r="AZ3" s="4">
+      <c r="S3" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA3" s="4">
+      <c r="T3" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC3" s="9">
+      <c r="U3" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V3" s="9">
         <v>374592</v>
       </c>
-      <c r="BD3" s="9">
+      <c r="W3" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE3" s="1"/>
-    </row>
-    <row r="4" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X3" s="1"/>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>34</v>
       </c>
@@ -1213,43 +1014,39 @@
         <v>2</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AG4"/>
-      <c r="AJ4"/>
-      <c r="AQ4"/>
-      <c r="AS4"/>
-      <c r="AV4" s="3">
+        <v>108</v>
+      </c>
+      <c r="O4" s="3">
         <v>45215.429189814815</v>
       </c>
-      <c r="AW4" s="3">
+      <c r="P4" s="3">
         <v>45216.665312500001</v>
       </c>
-      <c r="AX4" s="1">
+      <c r="Q4" s="1">
         <f t="shared" si="0"/>
         <v>29.666944444470573</v>
       </c>
-      <c r="AY4" s="1">
+      <c r="R4" s="1">
         <v>10</v>
       </c>
-      <c r="AZ4" s="4">
+      <c r="S4" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA4" s="4">
+      <c r="T4" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB4" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC4" s="9">
+      <c r="U4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V4" s="9">
         <v>374592</v>
       </c>
-      <c r="BD4" s="9">
+      <c r="W4" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE4" s="1"/>
-    </row>
-    <row r="5" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X4" s="1"/>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
@@ -1281,40 +1078,39 @@
         <v>100</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AQ5"/>
-      <c r="AV5" s="3">
+        <v>108</v>
+      </c>
+      <c r="O5" s="3">
         <v>45215.428969907407</v>
       </c>
-      <c r="AW5" s="3">
+      <c r="P5" s="3">
         <v>45216.741446759261</v>
       </c>
-      <c r="AX5" s="1">
+      <c r="Q5" s="1">
         <f t="shared" si="0"/>
         <v>31.4994444444892</v>
       </c>
-      <c r="AY5" s="1">
+      <c r="R5" s="1">
         <v>10</v>
       </c>
-      <c r="AZ5" s="4">
+      <c r="S5" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA5" s="4">
+      <c r="T5" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB5" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC5" s="9">
+      <c r="U5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V5" s="9">
         <v>374592</v>
       </c>
-      <c r="BD5" s="9">
+      <c r="W5" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE5" s="1"/>
-    </row>
-    <row r="6" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X5" s="1"/>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
@@ -1349,41 +1145,41 @@
         <v>2</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AV6" s="7">
+        <v>108</v>
+      </c>
+      <c r="O6" s="7">
         <v>45222.421354166669</v>
       </c>
-      <c r="AW6" s="7">
+      <c r="P6" s="7">
         <v>45223.442199074074</v>
       </c>
-      <c r="AX6" s="6">
+      <c r="Q6" s="6">
         <f t="shared" si="0"/>
         <v>24.500277777726296</v>
       </c>
-      <c r="AY6" s="6">
+      <c r="R6" s="6">
         <v>10</v>
       </c>
-      <c r="AZ6" s="4">
+      <c r="S6" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA6" s="4">
+      <c r="T6" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC6" s="9">
+      <c r="U6" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V6" s="9">
         <v>374592</v>
       </c>
-      <c r="BD6" s="9">
+      <c r="W6" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE6" s="6" t="s">
+      <c r="X6" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>34</v>
       </c>
@@ -1415,49 +1211,39 @@
         <v>100</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AI7"/>
-      <c r="AJ7"/>
-      <c r="AK7"/>
-      <c r="AL7"/>
-      <c r="AM7"/>
-      <c r="AN7"/>
-      <c r="AO7"/>
-      <c r="AR7"/>
-      <c r="AS7"/>
-      <c r="AT7"/>
-      <c r="AV7" s="3">
+        <v>108</v>
+      </c>
+      <c r="O7" s="3">
         <v>45222.420266203706</v>
       </c>
-      <c r="AW7" s="3">
-        <v>45222.593854166669</v>
-      </c>
-      <c r="AX7" s="4">
+      <c r="P7" s="3">
+        <v>45223.593854166669</v>
+      </c>
+      <c r="Q7" s="4">
         <f t="shared" si="0"/>
-        <v>4.1661111111170612</v>
-      </c>
-      <c r="AY7" s="4">
+        <v>28.166111111117061</v>
+      </c>
+      <c r="R7" s="4">
         <v>10</v>
       </c>
-      <c r="AZ7" s="4">
+      <c r="S7" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA7" s="4">
+      <c r="T7" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB7" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC7" s="9">
+      <c r="U7" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V7" s="9">
         <v>374592</v>
       </c>
-      <c r="BD7" s="9">
+      <c r="W7" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE7" s="1"/>
-    </row>
-    <row r="8" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X7" s="1"/>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>34</v>
       </c>
@@ -1492,63 +1278,39 @@
         <v>2</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="P8"/>
-      <c r="Q8"/>
-      <c r="R8"/>
-      <c r="S8"/>
-      <c r="T8"/>
-      <c r="U8"/>
-      <c r="V8"/>
-      <c r="W8"/>
-      <c r="AB8"/>
-      <c r="AC8"/>
-      <c r="AD8"/>
-      <c r="AF8"/>
-      <c r="AG8"/>
-      <c r="AH8"/>
-      <c r="AI8"/>
-      <c r="AJ8"/>
-      <c r="AK8"/>
-      <c r="AL8"/>
-      <c r="AM8"/>
-      <c r="AN8"/>
-      <c r="AO8"/>
-      <c r="AR8"/>
-      <c r="AS8"/>
-      <c r="AT8"/>
-      <c r="AV8" s="8">
+        <v>108</v>
+      </c>
+      <c r="O8" s="8">
         <v>45229.447210648148</v>
       </c>
-      <c r="AW8" s="8">
+      <c r="P8" s="8">
         <v>45230.495833333334</v>
       </c>
-      <c r="AX8" s="1">
+      <c r="Q8" s="1">
         <f t="shared" si="0"/>
         <v>25.166944444470573</v>
       </c>
-      <c r="AY8" s="1">
+      <c r="R8" s="1">
         <v>10</v>
       </c>
-      <c r="AZ8" s="4">
+      <c r="S8" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA8" s="4">
+      <c r="T8" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC8" s="9">
+      <c r="U8" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V8" s="9">
         <v>374592</v>
       </c>
-      <c r="BD8" s="9">
+      <c r="W8" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE8" s="1"/>
-    </row>
-    <row r="9" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X8" s="1"/>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
@@ -1580,65 +1342,41 @@
         <v>100</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="P9"/>
-      <c r="Q9"/>
-      <c r="R9"/>
-      <c r="S9"/>
-      <c r="T9"/>
-      <c r="U9"/>
-      <c r="V9"/>
-      <c r="W9"/>
-      <c r="AB9"/>
-      <c r="AC9"/>
-      <c r="AD9"/>
-      <c r="AF9"/>
-      <c r="AG9"/>
-      <c r="AH9"/>
-      <c r="AI9"/>
-      <c r="AJ9"/>
-      <c r="AK9"/>
-      <c r="AL9"/>
-      <c r="AM9"/>
-      <c r="AN9"/>
-      <c r="AO9"/>
-      <c r="AR9"/>
-      <c r="AS9"/>
-      <c r="AT9"/>
-      <c r="AV9" s="7">
+        <v>108</v>
+      </c>
+      <c r="O9" s="7">
         <v>45229.447569444441</v>
       </c>
-      <c r="AW9" s="7">
+      <c r="P9" s="7">
         <v>45230.468402777777</v>
       </c>
-      <c r="AX9" s="6">
+      <c r="Q9" s="6">
         <f t="shared" si="0"/>
         <v>24.500000000058208</v>
       </c>
-      <c r="AY9" s="6">
+      <c r="R9" s="6">
         <v>10</v>
       </c>
-      <c r="AZ9" s="4">
+      <c r="S9" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA9" s="4">
+      <c r="T9" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB9" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC9" s="9">
+      <c r="U9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V9" s="9">
         <v>374592</v>
       </c>
-      <c r="BD9" s="9">
+      <c r="W9" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE9" s="1" t="s">
+      <c r="X9" s="1" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>34</v>
       </c>
@@ -1673,60 +1411,39 @@
         <v>2</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="S10"/>
-      <c r="T10"/>
-      <c r="U10"/>
-      <c r="V10"/>
-      <c r="W10"/>
-      <c r="AB10"/>
-      <c r="AC10"/>
-      <c r="AD10"/>
-      <c r="AF10"/>
-      <c r="AG10"/>
-      <c r="AH10"/>
-      <c r="AI10"/>
-      <c r="AJ10"/>
-      <c r="AK10"/>
-      <c r="AL10"/>
-      <c r="AM10"/>
-      <c r="AN10"/>
-      <c r="AO10"/>
-      <c r="AR10"/>
-      <c r="AS10"/>
-      <c r="AT10"/>
-      <c r="AV10" s="8">
+        <v>108</v>
+      </c>
+      <c r="O10" s="8">
         <v>45236.461840277778</v>
       </c>
-      <c r="AW10" s="8">
+      <c r="P10" s="8">
         <v>45237.774363425924</v>
       </c>
-      <c r="AX10" s="1">
+      <c r="Q10" s="1">
         <f t="shared" si="0"/>
         <v>31.5005555555108</v>
       </c>
-      <c r="AY10" s="1">
+      <c r="R10" s="1">
         <v>10</v>
       </c>
-      <c r="AZ10" s="4">
+      <c r="S10" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA10" s="4">
+      <c r="T10" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC10" s="9">
+      <c r="U10" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V10" s="9">
         <v>374592</v>
       </c>
-      <c r="BD10" s="9">
+      <c r="W10" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE10" s="1"/>
-    </row>
-    <row r="11" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X10" s="1"/>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
@@ -1758,62 +1475,41 @@
         <v>100</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="P11"/>
-      <c r="Q11"/>
-      <c r="R11"/>
-      <c r="S11"/>
-      <c r="T11"/>
-      <c r="U11"/>
-      <c r="V11"/>
-      <c r="W11"/>
-      <c r="AB11"/>
-      <c r="AC11"/>
-      <c r="AD11"/>
-      <c r="AI11"/>
-      <c r="AJ11"/>
-      <c r="AK11"/>
-      <c r="AL11"/>
-      <c r="AM11"/>
-      <c r="AN11"/>
-      <c r="AO11"/>
-      <c r="AR11"/>
-      <c r="AS11"/>
-      <c r="AT11"/>
-      <c r="AV11" s="7">
+        <v>108</v>
+      </c>
+      <c r="O11" s="7">
         <v>45236.467731481483</v>
       </c>
-      <c r="AW11" s="7">
+      <c r="P11" s="7">
         <v>45237.731620370374</v>
       </c>
-      <c r="AX11" s="6">
+      <c r="Q11" s="6">
         <f t="shared" si="0"/>
         <v>30.333333333372138</v>
       </c>
-      <c r="AY11" s="6">
+      <c r="R11" s="6">
         <v>10</v>
       </c>
-      <c r="AZ11" s="4">
+      <c r="S11" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA11" s="4">
+      <c r="T11" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC11" s="9">
+      <c r="U11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V11" s="9">
         <v>374592</v>
       </c>
-      <c r="BD11" s="9">
+      <c r="W11" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE11" s="1" t="s">
+      <c r="X11" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>34</v>
       </c>
@@ -1848,53 +1544,41 @@
         <v>2</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="P12"/>
-      <c r="Q12"/>
-      <c r="R12"/>
-      <c r="S12"/>
-      <c r="T12"/>
-      <c r="U12"/>
-      <c r="V12"/>
-      <c r="W12"/>
-      <c r="AB12"/>
-      <c r="AC12"/>
-      <c r="AD12"/>
-      <c r="AE12"/>
-      <c r="AV12" s="8">
+        <v>108</v>
+      </c>
+      <c r="O12" s="8">
         <v>45243.473217592589</v>
       </c>
-      <c r="AW12" s="8">
+      <c r="P12" s="8">
         <v>45244.792685185188</v>
       </c>
-      <c r="AX12" s="1">
+      <c r="Q12" s="1">
         <f t="shared" si="0"/>
         <v>31.667222222371493</v>
       </c>
-      <c r="AY12" s="1">
+      <c r="R12" s="1">
         <v>10</v>
       </c>
-      <c r="AZ12" s="4">
+      <c r="S12" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA12" s="4">
+      <c r="T12" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC12" s="9">
+      <c r="U12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V12" s="9">
         <v>374592</v>
       </c>
-      <c r="BD12" s="9">
+      <c r="W12" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE12" s="13" t="s">
+      <c r="X12" s="13" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>34</v>
       </c>
@@ -1926,50 +1610,39 @@
         <v>100</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="S13"/>
-      <c r="T13"/>
-      <c r="U13"/>
-      <c r="V13"/>
-      <c r="W13"/>
-      <c r="AB13"/>
-      <c r="AC13"/>
-      <c r="AD13"/>
-      <c r="AF13"/>
-      <c r="AG13"/>
-      <c r="AH13"/>
-      <c r="AV13" s="8">
+        <v>108</v>
+      </c>
+      <c r="O13" s="8">
         <v>45243.477777777778</v>
       </c>
-      <c r="AW13" s="8">
+      <c r="P13" s="8">
         <v>45244.755532407406</v>
       </c>
-      <c r="AX13" s="1">
+      <c r="Q13" s="1">
         <f t="shared" si="0"/>
         <v>30.666111111058854</v>
       </c>
-      <c r="AY13" s="1">
+      <c r="R13" s="1">
         <v>10</v>
       </c>
-      <c r="AZ13" s="4">
+      <c r="S13" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA13" s="4">
+      <c r="T13" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC13" s="9">
+      <c r="U13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V13" s="9">
         <v>374592</v>
       </c>
-      <c r="BD13" s="9">
+      <c r="W13" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE13" s="1"/>
-    </row>
-    <row r="14" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X13" s="1"/>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>34</v>
       </c>
@@ -2004,41 +1677,39 @@
         <v>2</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AE14"/>
-      <c r="AP14"/>
-      <c r="AV14" s="8">
+        <v>108</v>
+      </c>
+      <c r="O14" s="8">
         <v>45250.50267361111</v>
       </c>
-      <c r="AW14" s="8">
+      <c r="P14" s="8">
         <v>45251.780462962961</v>
       </c>
-      <c r="AX14" s="1">
+      <c r="Q14" s="1">
         <f t="shared" si="0"/>
         <v>30.666944444412366</v>
       </c>
-      <c r="AY14" s="1">
+      <c r="R14" s="1">
         <v>10</v>
       </c>
-      <c r="AZ14" s="4">
+      <c r="S14" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA14" s="4">
+      <c r="T14" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC14" s="9">
+      <c r="U14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V14" s="9">
         <v>374592</v>
       </c>
-      <c r="BD14" s="9">
+      <c r="W14" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE14" s="1"/>
-    </row>
-    <row r="15" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X14" s="1"/>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>34</v>
       </c>
@@ -2070,57 +1741,39 @@
         <v>100</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="S15"/>
-      <c r="T15"/>
-      <c r="U15"/>
-      <c r="V15"/>
-      <c r="W15"/>
-      <c r="AF15"/>
-      <c r="AG15"/>
-      <c r="AH15"/>
-      <c r="AI15"/>
-      <c r="AJ15"/>
-      <c r="AK15"/>
-      <c r="AL15"/>
-      <c r="AM15"/>
-      <c r="AN15"/>
-      <c r="AO15"/>
-      <c r="AR15"/>
-      <c r="AS15"/>
-      <c r="AT15"/>
-      <c r="AV15" s="8">
+        <v>108</v>
+      </c>
+      <c r="O15" s="8">
         <v>45250.502696759257</v>
       </c>
-      <c r="AW15" s="8">
+      <c r="P15" s="8">
         <v>45251.73878472222</v>
       </c>
-      <c r="AX15" s="1">
+      <c r="Q15" s="1">
         <f t="shared" si="0"/>
         <v>29.666111111117061</v>
       </c>
-      <c r="AY15" s="1">
+      <c r="R15" s="1">
         <v>10</v>
       </c>
-      <c r="AZ15" s="4">
+      <c r="S15" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA15" s="4">
+      <c r="T15" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB15" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC15" s="9">
+      <c r="U15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V15" s="9">
         <v>374592</v>
       </c>
-      <c r="BD15" s="9">
+      <c r="W15" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE15" s="1"/>
-    </row>
-    <row r="16" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X15" s="1"/>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>34</v>
       </c>
@@ -2155,41 +1808,39 @@
         <v>2</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AE16"/>
-      <c r="AF16"/>
-      <c r="AV16" s="8">
+        <v>108</v>
+      </c>
+      <c r="O16" s="8">
         <v>45255.437245370369</v>
       </c>
-      <c r="AW16" s="8">
+      <c r="P16" s="8">
         <v>45256.742812500001</v>
       </c>
-      <c r="AX16" s="1">
+      <c r="Q16" s="1">
         <f t="shared" si="0"/>
         <v>31.333611111156642</v>
       </c>
-      <c r="AY16" s="1">
+      <c r="R16" s="1">
         <v>10</v>
       </c>
-      <c r="AZ16" s="4">
+      <c r="S16" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA16" s="4">
+      <c r="T16" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB16" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC16" s="9">
+      <c r="U16" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V16" s="9">
         <v>374592</v>
       </c>
-      <c r="BD16" s="9">
+      <c r="W16" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE16" s="1"/>
-    </row>
-    <row r="17" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X16" s="1"/>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>34</v>
       </c>
@@ -2221,40 +1872,39 @@
         <v>100</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AE17"/>
-      <c r="AV17" s="8">
+        <v>108</v>
+      </c>
+      <c r="O17" s="8">
         <v>45255.437592592592</v>
       </c>
-      <c r="AW17" s="8">
+      <c r="P17" s="8">
         <v>45256.694513888891</v>
       </c>
-      <c r="AX17" s="1">
+      <c r="Q17" s="1">
         <f t="shared" si="0"/>
         <v>30.166111111175269</v>
       </c>
-      <c r="AY17" s="1">
+      <c r="R17" s="1">
         <v>10</v>
       </c>
-      <c r="AZ17" s="4">
+      <c r="S17" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA17" s="4">
+      <c r="T17" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB17" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC17" s="9">
+      <c r="U17" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V17" s="9">
         <v>374592</v>
       </c>
-      <c r="BD17" s="9">
+      <c r="W17" s="9">
         <v>9959763</v>
       </c>
-      <c r="BE17" s="1"/>
-    </row>
-    <row r="18" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X17" s="1"/>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>34</v>
       </c>
@@ -2286,40 +1936,39 @@
         <v>100</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AE18"/>
-      <c r="AV18" s="8">
+        <v>108</v>
+      </c>
+      <c r="O18" s="8">
         <v>45255.453229166669</v>
       </c>
-      <c r="AW18" s="8">
+      <c r="P18" s="8">
         <v>45257.022685185184</v>
       </c>
-      <c r="AX18" s="1">
+      <c r="Q18" s="1">
         <f t="shared" si="0"/>
         <v>37.666944444354158</v>
       </c>
-      <c r="AY18" s="1">
+      <c r="R18" s="1">
         <v>10</v>
       </c>
-      <c r="AZ18" s="4">
+      <c r="S18" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA18" s="4">
+      <c r="T18" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB18" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC18" s="9">
+      <c r="U18" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V18" s="9">
         <v>374591</v>
       </c>
-      <c r="BD18" s="9">
+      <c r="W18" s="9">
         <v>9959822</v>
       </c>
-      <c r="BE18" s="1"/>
-    </row>
-    <row r="19" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X18" s="1"/>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>23</v>
       </c>
@@ -2354,41 +2003,41 @@
         <v>0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AV19" s="3">
+        <v>107</v>
+      </c>
+      <c r="O19" s="3">
         <v>45208.478182870371</v>
       </c>
-      <c r="AW19" s="3">
+      <c r="P19" s="3">
         <v>45209.742094907408</v>
       </c>
-      <c r="AX19" s="1">
+      <c r="Q19" s="1">
         <f t="shared" si="0"/>
         <v>30.333888888882939</v>
       </c>
-      <c r="AY19" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ19" s="4">
+      <c r="R19" s="1">
+        <v>100</v>
+      </c>
+      <c r="S19" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA19" s="4" t="s">
+      <c r="T19" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="BB19" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC19" s="9">
+      <c r="U19" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V19" s="9">
         <v>373860</v>
       </c>
-      <c r="BD19" s="9">
+      <c r="W19" s="9">
         <v>9959143</v>
       </c>
-      <c r="BE19" s="1" t="s">
+      <c r="X19" s="1" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="20" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
@@ -2419,39 +2068,39 @@
       <c r="J20" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="AV20" s="8">
+      <c r="O20" s="8">
         <v>45250.429039351853</v>
       </c>
-      <c r="AW20" s="8">
+      <c r="P20" s="8">
         <v>45251.748460648145</v>
       </c>
-      <c r="AX20" s="1">
+      <c r="Q20" s="1">
         <f t="shared" si="0"/>
         <v>31.666111111000646</v>
       </c>
-      <c r="AY20" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ20" s="4">
+      <c r="R20" s="1">
+        <v>100</v>
+      </c>
+      <c r="S20" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA20" s="4">
+      <c r="T20" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB20" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC20" s="4">
+      <c r="U20" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V20" s="4">
         <v>376986.5</v>
       </c>
-      <c r="BD20" s="4">
+      <c r="W20" s="4">
         <v>9962358</v>
       </c>
-      <c r="BE20" s="1" t="s">
+      <c r="X20" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="21" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>23</v>
       </c>
@@ -2482,37 +2131,37 @@
       <c r="J21" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AV21" s="8">
+      <c r="O21" s="8">
         <v>45250.450497685182</v>
       </c>
-      <c r="AW21" s="8">
+      <c r="P21" s="8">
         <v>45251.9921412037</v>
       </c>
-      <c r="AX21" s="1">
+      <c r="Q21" s="1">
         <f t="shared" si="0"/>
         <v>36.999444444430992</v>
       </c>
-      <c r="AY21" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ21" s="4">
+      <c r="R21" s="1">
+        <v>100</v>
+      </c>
+      <c r="S21" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA21" s="4">
+      <c r="T21" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB21" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC21" s="9">
+      <c r="U21" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V21" s="9">
         <v>380078</v>
       </c>
-      <c r="BD21" s="9">
+      <c r="W21" s="9">
         <v>9958544</v>
       </c>
-      <c r="BE21" s="1"/>
-    </row>
-    <row r="22" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X21" s="1"/>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,39 +2192,39 @@
       <c r="J22" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="AV22" s="8">
+      <c r="O22" s="8">
         <v>45250.460925925923</v>
       </c>
-      <c r="AW22" s="8">
+      <c r="P22" s="8">
         <v>45251.752581018518</v>
       </c>
-      <c r="AX22" s="1">
+      <c r="Q22" s="1">
         <f t="shared" si="0"/>
         <v>30.999722222273704</v>
       </c>
-      <c r="AY22" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ22" s="4" t="s">
+      <c r="R22" s="1">
+        <v>100</v>
+      </c>
+      <c r="S22" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="BA22" s="4" t="s">
+      <c r="T22" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="BB22" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC22" s="9">
+      <c r="U22" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V22" s="9">
         <v>380002.5</v>
       </c>
-      <c r="BD22" s="9">
+      <c r="W22" s="9">
         <v>9958606</v>
       </c>
-      <c r="BE22" s="1" t="s">
+      <c r="X22" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>23</v>
       </c>
@@ -2606,37 +2255,37 @@
       <c r="J23" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AV23" s="8">
+      <c r="O23" s="8">
         <v>45250.477164351854</v>
       </c>
-      <c r="AW23" s="8">
+      <c r="P23" s="8">
         <v>45252.067442129628</v>
       </c>
-      <c r="AX23" s="1">
+      <c r="Q23" s="1">
         <f t="shared" si="0"/>
         <v>38.166666666569654</v>
       </c>
-      <c r="AY23" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ23" s="4">
+      <c r="R23" s="1">
+        <v>100</v>
+      </c>
+      <c r="S23" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA23" s="4">
+      <c r="T23" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB23" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC23" s="9">
+      <c r="U23" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V23" s="9">
         <v>378278</v>
       </c>
-      <c r="BD23" s="9">
+      <c r="W23" s="9">
         <v>9957271</v>
       </c>
-      <c r="BE23" s="1"/>
-    </row>
-    <row r="24" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X23" s="1"/>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>23</v>
       </c>
@@ -2667,39 +2316,39 @@
       <c r="J24" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="AV24" s="8">
+      <c r="O24" s="8">
         <v>45255.393958333334</v>
       </c>
-      <c r="AW24" s="8">
+      <c r="P24" s="8">
         <v>45256.70648148148</v>
       </c>
-      <c r="AX24" s="1">
+      <c r="Q24" s="1">
         <f t="shared" si="0"/>
         <v>31.5005555555108</v>
       </c>
-      <c r="AY24" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ24" s="4">
+      <c r="R24" s="1">
+        <v>100</v>
+      </c>
+      <c r="S24" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA24" s="4">
+      <c r="T24" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC24" s="9">
+      <c r="U24" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V24" s="9">
         <v>378529</v>
       </c>
-      <c r="BD24" s="9">
+      <c r="W24" s="9">
         <v>9960571</v>
       </c>
-      <c r="BE24" s="1" t="s">
+      <c r="X24" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="25" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
@@ -2730,39 +2379,39 @@
       <c r="J25" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="AV25" s="8">
+      <c r="O25" s="8">
         <v>45255.410949074074</v>
       </c>
-      <c r="AW25" s="8">
+      <c r="P25" s="8">
         <v>45256.959537037037</v>
       </c>
-      <c r="AX25" s="1">
+      <c r="Q25" s="1">
         <f t="shared" si="0"/>
         <v>37.166111111117061</v>
       </c>
-      <c r="AY25" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ25" s="4">
+      <c r="R25" s="1">
+        <v>100</v>
+      </c>
+      <c r="S25" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA25" s="4">
+      <c r="T25" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB25" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC25" s="9">
+      <c r="U25" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V25" s="9">
         <v>375916</v>
       </c>
-      <c r="BD25" s="9">
+      <c r="W25" s="9">
         <v>9958544</v>
       </c>
-      <c r="BE25" s="1" t="s">
+      <c r="X25" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>23</v>
       </c>
@@ -2793,39 +2442,39 @@
       <c r="J26" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AV26" s="8">
+      <c r="O26" s="8">
         <v>45255.487893518519</v>
       </c>
-      <c r="AW26" s="8">
+      <c r="P26" s="8">
         <v>45256.710104166668</v>
       </c>
-      <c r="AX26" s="1">
+      <c r="Q26" s="1">
         <f t="shared" si="0"/>
         <v>29.333055555587634</v>
       </c>
-      <c r="AY26" s="1">
+      <c r="R26" s="1">
         <v>10</v>
       </c>
-      <c r="AZ26" s="4" t="s">
+      <c r="S26" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="BA26" s="4" t="s">
+      <c r="T26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="BB26" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC26" s="9">
+      <c r="U26" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V26" s="9">
         <v>374826</v>
       </c>
-      <c r="BD26" s="9">
+      <c r="W26" s="9">
         <v>9960108</v>
       </c>
-      <c r="BE26" s="1" t="s">
+      <c r="X26" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="27" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>23</v>
       </c>
@@ -2860,44 +2509,44 @@
         <v>7</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="AV27" s="3">
+        <v>109</v>
+      </c>
+      <c r="O27" s="3">
         <v>45215.400196759256</v>
       </c>
-      <c r="AW27" s="3">
+      <c r="P27" s="3">
         <v>45216.7266087963</v>
       </c>
-      <c r="AX27" s="1">
+      <c r="Q27" s="1">
         <f t="shared" si="0"/>
         <v>31.833888889057562</v>
       </c>
-      <c r="AY27" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ27" s="4">
+      <c r="R27" s="1">
+        <v>100</v>
+      </c>
+      <c r="S27" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA27" s="4" t="s">
+      <c r="T27" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="BB27" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC27" s="9">
+      <c r="U27" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V27" s="9">
         <v>374320</v>
       </c>
-      <c r="BD27" s="9">
+      <c r="W27" s="9">
         <v>9957429</v>
       </c>
-      <c r="BE27" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="28" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X27" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2928,39 +2577,39 @@
       <c r="J28" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AV28" s="8">
+      <c r="O28" s="8">
         <v>45222.398206018515</v>
       </c>
-      <c r="AW28" s="8">
+      <c r="P28" s="8">
         <v>45223.467673611114</v>
       </c>
-      <c r="AX28" s="1">
+      <c r="Q28" s="1">
         <f t="shared" si="0"/>
         <v>25.667222222371493</v>
       </c>
-      <c r="AY28" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ28" s="4">
+      <c r="R28" s="1">
+        <v>100</v>
+      </c>
+      <c r="S28" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA28" s="4">
+      <c r="T28" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB28" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC28" s="9">
+      <c r="U28" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V28" s="9">
         <v>374584</v>
       </c>
-      <c r="BD28" s="9">
+      <c r="W28" s="9">
         <v>9959720</v>
       </c>
-      <c r="BE28" s="12" t="s">
+      <c r="X28" s="12" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="29" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>23</v>
       </c>
@@ -2991,39 +2640,39 @@
       <c r="J29" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AV29" s="7">
+      <c r="O29" s="7">
         <v>45229.42701388889</v>
       </c>
-      <c r="AW29" s="7">
+      <c r="P29" s="7">
         <v>45230.496458333335</v>
       </c>
-      <c r="AX29" s="6">
+      <c r="Q29" s="6">
         <f t="shared" si="0"/>
         <v>25.666666666686069</v>
       </c>
-      <c r="AY29" s="6">
-        <v>100</v>
-      </c>
-      <c r="AZ29" s="4">
+      <c r="R29" s="6">
+        <v>100</v>
+      </c>
+      <c r="S29" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA29" s="4">
+      <c r="T29" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB29" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC29" s="9">
+      <c r="U29" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V29" s="9">
         <v>374467</v>
       </c>
-      <c r="BD29" s="9">
+      <c r="W29" s="9">
         <v>9959722</v>
       </c>
-      <c r="BE29" s="1" t="s">
+      <c r="X29" s="1" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="30" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>23</v>
       </c>
@@ -3054,37 +2703,37 @@
       <c r="J30" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AV30" s="8">
+      <c r="O30" s="8">
         <v>45236.390798611108</v>
       </c>
-      <c r="AW30" s="8">
+      <c r="P30" s="8">
         <v>45237.717164351852</v>
       </c>
-      <c r="AX30" s="1">
+      <c r="Q30" s="1">
         <f t="shared" si="0"/>
         <v>31.832777777861338</v>
       </c>
-      <c r="AY30" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ30" s="4">
+      <c r="R30" s="1">
+        <v>100</v>
+      </c>
+      <c r="S30" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA30" s="4">
+      <c r="T30" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB30" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC30" s="9">
+      <c r="U30" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V30" s="9">
         <v>381026</v>
       </c>
-      <c r="BD30" s="9">
+      <c r="W30" s="9">
         <v>9962052</v>
       </c>
-      <c r="BE30" s="1"/>
-    </row>
-    <row r="31" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X30" s="1"/>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>23</v>
       </c>
@@ -3115,37 +2764,37 @@
       <c r="J31" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AV31" s="8">
+      <c r="O31" s="8">
         <v>45236.40483796296</v>
       </c>
-      <c r="AW31" s="8">
+      <c r="P31" s="8">
         <v>45237.745138888888</v>
       </c>
-      <c r="AX31" s="1">
+      <c r="Q31" s="1">
         <f t="shared" si="0"/>
         <v>32.167222222255077</v>
       </c>
-      <c r="AY31" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ31" s="4">
+      <c r="R31" s="1">
+        <v>100</v>
+      </c>
+      <c r="S31" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA31" s="4">
+      <c r="T31" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB31" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC31" s="9">
+      <c r="U31" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V31" s="9">
         <v>381086</v>
       </c>
-      <c r="BD31" s="9">
+      <c r="W31" s="9">
         <v>9962037</v>
       </c>
-      <c r="BE31" s="1"/>
-    </row>
-    <row r="32" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X31" s="1"/>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>23</v>
       </c>
@@ -3176,37 +2825,37 @@
       <c r="J32" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AV32" s="8">
+      <c r="O32" s="8">
         <v>45243.434733796297</v>
       </c>
-      <c r="AW32" s="8">
+      <c r="P32" s="8">
         <v>45244.78197916667</v>
       </c>
-      <c r="AX32" s="1">
+      <c r="Q32" s="1">
         <f t="shared" si="0"/>
         <v>32.333888888941146</v>
       </c>
-      <c r="AY32" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ32" s="4">
+      <c r="R32" s="1">
+        <v>100</v>
+      </c>
+      <c r="S32" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA32" s="4">
+      <c r="T32" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB32" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC32" s="9">
+      <c r="U32" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V32" s="9">
         <v>379010</v>
       </c>
-      <c r="BD32" s="9">
+      <c r="W32" s="9">
         <v>9962442</v>
       </c>
-      <c r="BE32" s="1"/>
-    </row>
-    <row r="33" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X32" s="1"/>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>23</v>
       </c>
@@ -3237,39 +2886,39 @@
       <c r="J33" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="AV33" s="8">
+      <c r="O33" s="8">
         <v>45243.42224537037</v>
       </c>
-      <c r="AW33" s="8">
+      <c r="P33" s="8">
         <v>45244.741678240738</v>
       </c>
-      <c r="AX33" s="1">
+      <c r="Q33" s="1">
         <f t="shared" si="0"/>
         <v>31.666388888843358</v>
       </c>
-      <c r="AY33" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ33" s="4">
+      <c r="R33" s="1">
+        <v>100</v>
+      </c>
+      <c r="S33" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA33" s="4">
+      <c r="T33" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB33" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC33" s="9">
+      <c r="U33" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V33" s="9">
         <v>380983</v>
       </c>
-      <c r="BD33" s="9">
+      <c r="W33" s="9">
         <v>9961970</v>
       </c>
-      <c r="BE33" s="13" t="s">
+      <c r="X33" s="13" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="34" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>23</v>
       </c>
@@ -3300,37 +2949,37 @@
       <c r="J34" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="AV34" s="8">
+      <c r="O34" s="8">
         <v>45250.414780092593</v>
       </c>
-      <c r="AW34" s="8">
+      <c r="P34" s="8">
         <v>45251.762025462966</v>
       </c>
-      <c r="AX34" s="1">
-        <f t="shared" ref="AX34:AX65" si="1">(AW34-AV34)*24</f>
+      <c r="Q34" s="1">
+        <f t="shared" ref="Q34:Q65" si="1">(P34-O34)*24</f>
         <v>32.333888888941146</v>
       </c>
-      <c r="AY34" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ34" s="4">
+      <c r="R34" s="1">
+        <v>100</v>
+      </c>
+      <c r="S34" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA34" s="4">
+      <c r="T34" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB34" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC34" s="9">
+      <c r="U34" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V34" s="9">
         <v>376926</v>
       </c>
-      <c r="BD34" s="9">
+      <c r="W34" s="9">
         <v>9962491</v>
       </c>
-      <c r="BE34" s="1"/>
-    </row>
-    <row r="35" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X34" s="1"/>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>23</v>
       </c>
@@ -3362,39 +3011,39 @@
         <v>100</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="AV35" s="3">
+        <v>107</v>
+      </c>
+      <c r="O35" s="3">
         <v>45222.367615740739</v>
       </c>
-      <c r="AW35" s="3">
+      <c r="P35" s="3">
         <v>45223.228715277779</v>
       </c>
-      <c r="AX35" s="1">
+      <c r="Q35" s="1">
         <f t="shared" si="1"/>
         <v>20.666388888959773</v>
       </c>
-      <c r="AY35" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ35" s="4" t="s">
+      <c r="R35" s="1">
+        <v>100</v>
+      </c>
+      <c r="S35" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="BA35" s="4" t="s">
+      <c r="T35" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="BB35" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC35" s="9">
+      <c r="U35" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V35" s="9">
         <v>374619</v>
       </c>
-      <c r="BD35" s="9">
+      <c r="W35" s="9">
         <v>9959621</v>
       </c>
-      <c r="BE35" s="1"/>
-    </row>
-    <row r="36" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X35" s="1"/>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>23</v>
       </c>
@@ -3425,37 +3074,37 @@
       <c r="J36" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="AV36" s="8">
+      <c r="O36" s="8">
         <v>45229.393912037034</v>
       </c>
-      <c r="AW36" s="8">
+      <c r="P36" s="8">
         <v>45230.664733796293</v>
       </c>
-      <c r="AX36" s="1">
+      <c r="Q36" s="1">
         <f t="shared" si="1"/>
         <v>30.499722222215496</v>
       </c>
-      <c r="AY36" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ36" s="4">
+      <c r="R36" s="1">
+        <v>100</v>
+      </c>
+      <c r="S36" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA36" s="4">
+      <c r="T36" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB36" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC36" s="9">
+      <c r="U36" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V36" s="9">
         <v>374705</v>
       </c>
-      <c r="BD36" s="9">
+      <c r="W36" s="9">
         <v>9959456</v>
       </c>
-      <c r="BE36" s="1"/>
-    </row>
-    <row r="37" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X36" s="1"/>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>23</v>
       </c>
@@ -3486,37 +3135,37 @@
       <c r="J37" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="AV37" s="8">
+      <c r="O37" s="8">
         <v>45236.4530787037</v>
       </c>
-      <c r="AW37" s="8">
+      <c r="P37" s="8">
         <v>45237.966944444444</v>
       </c>
-      <c r="AX37" s="1">
+      <c r="Q37" s="1">
         <f t="shared" si="1"/>
         <v>36.332777777861338</v>
       </c>
-      <c r="AY37" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ37" s="4">
+      <c r="R37" s="1">
+        <v>100</v>
+      </c>
+      <c r="S37" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA37" s="4">
+      <c r="T37" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB37" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC37" s="4">
+      <c r="U37" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V37" s="4">
         <v>374819.5</v>
       </c>
-      <c r="BD37" s="4">
+      <c r="W37" s="4">
         <v>9959335</v>
       </c>
-      <c r="BE37" s="1"/>
-    </row>
-    <row r="38" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X37" s="1"/>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>23</v>
       </c>
@@ -3547,37 +3196,37 @@
       <c r="J38" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="AV38" s="8">
+      <c r="O38" s="8">
         <v>45243.458460648151</v>
       </c>
-      <c r="AW38" s="8">
+      <c r="P38" s="8">
         <v>45245.000115740739</v>
       </c>
-      <c r="AX38" s="1">
+      <c r="Q38" s="1">
         <f t="shared" si="1"/>
         <v>36.999722222099081</v>
       </c>
-      <c r="AY38" s="1">
-        <v>100</v>
-      </c>
-      <c r="AZ38" s="4">
+      <c r="R38" s="1">
+        <v>100</v>
+      </c>
+      <c r="S38" s="4">
         <v>0.02</v>
       </c>
-      <c r="BA38" s="4">
+      <c r="T38" s="4">
         <v>0.02</v>
       </c>
-      <c r="BB38" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC38" s="4">
+      <c r="U38" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V38" s="4">
         <v>374886</v>
       </c>
-      <c r="BD38" s="4">
+      <c r="W38" s="4">
         <v>9959269</v>
       </c>
-      <c r="BE38" s="1"/>
-    </row>
-    <row r="39" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X38" s="1"/>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>12</v>
       </c>
@@ -3609,39 +3258,39 @@
         <v>100</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV39" s="3">
+        <v>110</v>
+      </c>
+      <c r="O39" s="3">
         <v>45217.540046296293</v>
       </c>
-      <c r="AW39" s="3">
+      <c r="P39" s="3">
         <v>45218.810856481483</v>
       </c>
-      <c r="AX39" s="1">
+      <c r="Q39" s="1">
         <f t="shared" si="1"/>
         <v>30.499444444547407</v>
       </c>
-      <c r="AY39" s="1">
+      <c r="R39" s="1">
         <v>10</v>
       </c>
-      <c r="AZ39" s="4">
+      <c r="S39" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA39" s="4">
+      <c r="T39" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB39" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC39" s="9">
+      <c r="U39" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V39" s="9">
         <v>382794</v>
       </c>
-      <c r="BD39" s="9">
+      <c r="W39" s="9">
         <v>9964774</v>
       </c>
-      <c r="BE39" s="1"/>
-    </row>
-    <row r="40" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X39" s="1"/>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>12</v>
       </c>
@@ -3673,39 +3322,39 @@
         <v>100</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV40" s="3">
+        <v>110</v>
+      </c>
+      <c r="O40" s="3">
         <v>45217.540162037039</v>
       </c>
-      <c r="AW40" s="3">
+      <c r="P40" s="3">
         <v>45218.852685185186</v>
       </c>
-      <c r="AX40" s="1">
+      <c r="Q40" s="1">
         <f t="shared" si="1"/>
         <v>31.5005555555108</v>
       </c>
-      <c r="AY40" s="1">
+      <c r="R40" s="1">
         <v>10</v>
       </c>
-      <c r="AZ40" s="4">
+      <c r="S40" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA40" s="4">
+      <c r="T40" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB40" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC40" s="9">
+      <c r="U40" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V40" s="9">
         <v>382794</v>
       </c>
-      <c r="BD40" s="9">
+      <c r="W40" s="9">
         <v>9964774</v>
       </c>
-      <c r="BE40" s="1"/>
-    </row>
-    <row r="41" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X40" s="1"/>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>12</v>
       </c>
@@ -3737,39 +3386,39 @@
         <v>100</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV41" s="8">
+        <v>110</v>
+      </c>
+      <c r="O41" s="8">
         <v>45224.524004629631</v>
       </c>
-      <c r="AW41" s="8">
+      <c r="P41" s="8">
         <v>45225.565659722219</v>
       </c>
-      <c r="AX41" s="1">
+      <c r="Q41" s="1">
         <f t="shared" si="1"/>
         <v>24.999722222099081</v>
       </c>
-      <c r="AY41" s="1">
+      <c r="R41" s="1">
         <v>10</v>
       </c>
-      <c r="AZ41" s="4">
+      <c r="S41" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA41" s="4">
+      <c r="T41" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB41" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC41" s="9">
+      <c r="U41" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V41" s="9">
         <v>382794</v>
       </c>
-      <c r="BD41" s="9">
+      <c r="W41" s="9">
         <v>9964774</v>
       </c>
-      <c r="BE41" s="1"/>
-    </row>
-    <row r="42" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X41" s="1"/>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>12</v>
       </c>
@@ -3801,39 +3450,39 @@
         <v>100</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV42" s="8">
+        <v>110</v>
+      </c>
+      <c r="O42" s="8">
         <v>45224.521956018521</v>
       </c>
-      <c r="AW42" s="8">
+      <c r="P42" s="8">
         <v>45225.549722222226</v>
       </c>
-      <c r="AX42" s="1">
+      <c r="Q42" s="1">
         <f t="shared" si="1"/>
         <v>24.666388888901565</v>
       </c>
-      <c r="AY42" s="1">
+      <c r="R42" s="1">
         <v>10</v>
       </c>
-      <c r="AZ42" s="4">
+      <c r="S42" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA42" s="4">
+      <c r="T42" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB42" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC42" s="9">
+      <c r="U42" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V42" s="9">
         <v>382794</v>
       </c>
-      <c r="BD42" s="9">
+      <c r="W42" s="9">
         <v>9964774</v>
       </c>
-      <c r="BE42" s="1"/>
-    </row>
-    <row r="43" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X42" s="1"/>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>12</v>
       </c>
@@ -3865,39 +3514,39 @@
         <v>100</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV43" s="8">
+        <v>110</v>
+      </c>
+      <c r="O43" s="8">
         <v>45231.509120370371</v>
       </c>
-      <c r="AW43" s="8">
+      <c r="P43" s="8">
         <v>45232.578553240739</v>
       </c>
-      <c r="AX43" s="1">
+      <c r="Q43" s="1">
         <f t="shared" si="1"/>
         <v>25.666388888843358</v>
       </c>
-      <c r="AY43" s="1">
+      <c r="R43" s="1">
         <v>10</v>
       </c>
-      <c r="AZ43" s="4">
+      <c r="S43" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA43" s="4">
+      <c r="T43" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB43" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC43" s="9">
+      <c r="U43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V43" s="9">
         <v>382794</v>
       </c>
-      <c r="BD43" s="9">
+      <c r="W43" s="9">
         <v>9964774</v>
       </c>
-      <c r="BE43" s="1"/>
-    </row>
-    <row r="44" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X43" s="1"/>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>12</v>
       </c>
@@ -3929,41 +3578,41 @@
         <v>100</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV44" s="7">
+        <v>110</v>
+      </c>
+      <c r="O44" s="7">
         <v>45231.509016203701</v>
       </c>
-      <c r="AW44" s="7">
+      <c r="P44" s="7">
         <v>45232.542997685188</v>
       </c>
-      <c r="AX44" s="6">
+      <c r="Q44" s="6">
         <f t="shared" si="1"/>
         <v>24.815555555687752</v>
       </c>
-      <c r="AY44" s="6">
+      <c r="R44" s="6">
         <v>10</v>
       </c>
-      <c r="AZ44" s="4">
+      <c r="S44" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA44" s="4">
+      <c r="T44" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB44" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC44" s="9">
+      <c r="U44" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V44" s="9">
         <v>382794</v>
       </c>
-      <c r="BD44" s="9">
+      <c r="W44" s="9">
         <v>9964774</v>
       </c>
-      <c r="BE44" s="1" t="s">
+      <c r="X44" s="1" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="45" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>12</v>
       </c>
@@ -3995,39 +3644,39 @@
         <v>100</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV45" s="8">
+        <v>110</v>
+      </c>
+      <c r="O45" s="8">
         <v>45238.506041666667</v>
       </c>
-      <c r="AW45" s="8">
+      <c r="P45" s="8">
         <v>45239.860196759262</v>
       </c>
-      <c r="AX45" s="1">
+      <c r="Q45" s="1">
         <f t="shared" si="1"/>
         <v>32.499722222273704</v>
       </c>
-      <c r="AY45" s="1">
+      <c r="R45" s="1">
         <v>10</v>
       </c>
-      <c r="AZ45" s="4">
+      <c r="S45" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA45" s="4">
+      <c r="T45" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB45" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC45" s="9">
+      <c r="U45" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V45" s="9">
         <v>382794</v>
       </c>
-      <c r="BD45" s="9">
+      <c r="W45" s="9">
         <v>9964774</v>
       </c>
-      <c r="BE45" s="1"/>
-    </row>
-    <row r="46" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X45" s="1"/>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>12</v>
       </c>
@@ -4059,41 +3708,41 @@
         <v>100</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV46" s="7">
+        <v>110</v>
+      </c>
+      <c r="O46" s="7">
         <v>45238.508715277778</v>
       </c>
-      <c r="AW46" s="7">
+      <c r="P46" s="7">
         <v>45239.682326388887</v>
       </c>
-      <c r="AX46" s="6">
+      <c r="Q46" s="6">
         <f t="shared" si="1"/>
         <v>28.166666666627862</v>
       </c>
-      <c r="AY46" s="6">
+      <c r="R46" s="6">
         <v>10</v>
       </c>
-      <c r="AZ46" s="4">
+      <c r="S46" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA46" s="4">
+      <c r="T46" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB46" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC46" s="9">
+      <c r="U46" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V46" s="9">
         <v>382794</v>
       </c>
-      <c r="BD46" s="9">
+      <c r="W46" s="9">
         <v>9964774</v>
       </c>
-      <c r="BE46" s="1" t="s">
+      <c r="X46" s="1" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="47" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>12</v>
       </c>
@@ -4125,41 +3774,41 @@
         <v>100</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV47" s="8">
+        <v>110</v>
+      </c>
+      <c r="O47" s="8">
         <v>45245.554861111108</v>
       </c>
-      <c r="AW47" s="8">
+      <c r="P47" s="8">
         <v>45246.832627314812</v>
       </c>
-      <c r="AX47" s="1">
+      <c r="Q47" s="1">
         <f t="shared" si="1"/>
         <v>30.666388888901565</v>
       </c>
-      <c r="AY47" s="1">
+      <c r="R47" s="1">
         <v>10</v>
       </c>
-      <c r="AZ47" s="4">
+      <c r="S47" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA47" s="4">
+      <c r="T47" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB47" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC47" s="9">
+      <c r="U47" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V47" s="9">
         <v>382794</v>
       </c>
-      <c r="BD47" s="9">
+      <c r="W47" s="9">
         <v>9964774</v>
       </c>
-      <c r="BE47" s="1" t="s">
+      <c r="X47" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="48" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>12</v>
       </c>
@@ -4191,41 +3840,41 @@
         <v>100</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV48" s="7">
+        <v>110</v>
+      </c>
+      <c r="O48" s="7">
         <v>45252.645624999997</v>
       </c>
-      <c r="AW48" s="7">
+      <c r="P48" s="7">
         <v>45253.992835648147</v>
       </c>
-      <c r="AX48" s="6">
+      <c r="Q48" s="6">
         <f t="shared" si="1"/>
         <v>32.333055555587634</v>
       </c>
-      <c r="AY48" s="6">
+      <c r="R48" s="6">
         <v>10</v>
       </c>
-      <c r="AZ48" s="4">
+      <c r="S48" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA48" s="4">
+      <c r="T48" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB48" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC48" s="9">
+      <c r="U48" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V48" s="9">
         <v>382794</v>
       </c>
-      <c r="BD48" s="9">
+      <c r="W48" s="9">
         <v>9964774</v>
       </c>
-      <c r="BE48" s="6" t="s">
+      <c r="X48" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>12</v>
       </c>
@@ -4257,41 +3906,41 @@
         <v>100</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV49" s="7">
+        <v>110</v>
+      </c>
+      <c r="O49" s="7">
         <v>45252.64565972222</v>
       </c>
-      <c r="AW49" s="7">
+      <c r="P49" s="7">
         <v>45253.916481481479</v>
       </c>
-      <c r="AX49" s="6">
+      <c r="Q49" s="6">
         <f t="shared" si="1"/>
         <v>30.499722222215496</v>
       </c>
-      <c r="AY49" s="6">
+      <c r="R49" s="6">
         <v>10</v>
       </c>
-      <c r="AZ49" s="4">
+      <c r="S49" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA49" s="4">
+      <c r="T49" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB49" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC49" s="9">
+      <c r="U49" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V49" s="9">
         <v>382794</v>
       </c>
-      <c r="BD49" s="9">
+      <c r="W49" s="9">
         <v>9964774</v>
       </c>
-      <c r="BE49" s="6" t="s">
+      <c r="X49" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>12</v>
       </c>
@@ -4323,39 +3972,39 @@
         <v>100</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV50" s="8">
+        <v>110</v>
+      </c>
+      <c r="O50" s="8">
         <v>45257.568749999999</v>
       </c>
-      <c r="AW50" s="8">
+      <c r="P50" s="8">
         <v>45258.881238425929</v>
       </c>
-      <c r="AX50" s="1">
+      <c r="Q50" s="1">
         <f t="shared" si="1"/>
         <v>31.499722222331911</v>
       </c>
-      <c r="AY50" s="1">
+      <c r="R50" s="1">
         <v>10</v>
       </c>
-      <c r="AZ50" s="4">
+      <c r="S50" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA50" s="4">
+      <c r="T50" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB50" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC50" s="9">
+      <c r="U50" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V50" s="9">
         <v>382794</v>
       </c>
-      <c r="BD50" s="9">
+      <c r="W50" s="9">
         <v>9964774</v>
       </c>
-      <c r="BE50" s="1"/>
-    </row>
-    <row r="51" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X50" s="1"/>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>12</v>
       </c>
@@ -4387,39 +4036,39 @@
         <v>100</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV51" s="8">
+        <v>110</v>
+      </c>
+      <c r="O51" s="8">
         <v>45257.570370370369</v>
       </c>
-      <c r="AW51" s="8">
+      <c r="P51" s="8">
         <v>45258.841192129628</v>
       </c>
-      <c r="AX51" s="1">
+      <c r="Q51" s="1">
         <f t="shared" si="1"/>
         <v>30.499722222215496</v>
       </c>
-      <c r="AY51" s="1">
+      <c r="R51" s="1">
         <v>10</v>
       </c>
-      <c r="AZ51" s="4">
+      <c r="S51" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA51" s="4">
+      <c r="T51" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB51" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC51" s="9">
+      <c r="U51" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V51" s="9">
         <v>382794</v>
       </c>
-      <c r="BD51" s="9">
+      <c r="W51" s="9">
         <v>9964774</v>
       </c>
-      <c r="BE51" s="1"/>
-    </row>
-    <row r="52" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X51" s="1"/>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>12</v>
       </c>
@@ -4450,37 +4099,37 @@
       <c r="J52" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="AV52" s="3">
+      <c r="O52" s="3">
         <v>45217.554155092592</v>
       </c>
-      <c r="AW52" s="3">
+      <c r="P52" s="3">
         <v>45218.394421296296</v>
       </c>
-      <c r="AX52" s="1">
+      <c r="Q52" s="1">
         <f t="shared" si="1"/>
         <v>20.166388888901565</v>
       </c>
-      <c r="AY52" s="1">
+      <c r="R52" s="1">
         <v>10</v>
       </c>
-      <c r="AZ52" s="4">
+      <c r="S52" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA52" s="4">
+      <c r="T52" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB52" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC52" s="9">
+      <c r="U52" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V52" s="9">
         <v>382782</v>
       </c>
-      <c r="BD52" s="9">
+      <c r="W52" s="9">
         <v>9964814</v>
       </c>
-      <c r="BE52" s="1"/>
-    </row>
-    <row r="53" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X52" s="1"/>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>12</v>
       </c>
@@ -4511,39 +4160,39 @@
       <c r="J53" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="AV53" s="7">
+      <c r="O53" s="7">
         <v>45224.532442129632</v>
       </c>
-      <c r="AW53" s="7">
+      <c r="P53" s="7">
         <v>45225.171342592592</v>
       </c>
-      <c r="AX53" s="6">
+      <c r="Q53" s="6">
         <f t="shared" si="1"/>
         <v>15.333611111040227</v>
       </c>
-      <c r="AY53" s="6">
+      <c r="R53" s="6">
         <v>10</v>
       </c>
-      <c r="AZ53" s="4">
+      <c r="S53" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA53" s="4">
+      <c r="T53" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB53" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC53" s="9">
+      <c r="U53" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V53" s="9">
         <v>382782</v>
       </c>
-      <c r="BD53" s="9">
+      <c r="W53" s="9">
         <v>9964814</v>
       </c>
-      <c r="BE53" s="1" t="s">
+      <c r="X53" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="54" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>12</v>
       </c>
@@ -4574,37 +4223,37 @@
       <c r="J54" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="AV54" s="8">
+      <c r="O54" s="8">
         <v>45231.517847222225</v>
       </c>
-      <c r="AW54" s="8">
+      <c r="P54" s="8">
         <v>45232.58730324074</v>
       </c>
-      <c r="AX54" s="1">
+      <c r="Q54" s="1">
         <f t="shared" si="1"/>
         <v>25.666944444354158</v>
       </c>
-      <c r="AY54" s="1">
+      <c r="R54" s="1">
         <v>10</v>
       </c>
-      <c r="AZ54" s="4">
+      <c r="S54" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA54" s="4">
+      <c r="T54" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB54" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC54" s="9">
+      <c r="U54" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V54" s="9">
         <v>382782</v>
       </c>
-      <c r="BD54" s="9">
+      <c r="W54" s="9">
         <v>9964814</v>
       </c>
-      <c r="BE54" s="1"/>
-    </row>
-    <row r="55" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X54" s="1"/>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>12</v>
       </c>
@@ -4635,37 +4284,37 @@
       <c r="J55" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="AV55" s="8">
+      <c r="O55" s="8">
         <v>45238.512407407405</v>
       </c>
-      <c r="AW55" s="8">
+      <c r="P55" s="8">
         <v>45239.824930555558</v>
       </c>
-      <c r="AX55" s="1">
+      <c r="Q55" s="1">
         <f t="shared" si="1"/>
         <v>31.500555555685423</v>
       </c>
-      <c r="AY55" s="1">
+      <c r="R55" s="1">
         <v>10</v>
       </c>
-      <c r="AZ55" s="4">
+      <c r="S55" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA55" s="4">
+      <c r="T55" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB55" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC55" s="9">
+      <c r="U55" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V55" s="9">
         <v>382782</v>
       </c>
-      <c r="BD55" s="9">
+      <c r="W55" s="9">
         <v>9964814</v>
       </c>
-      <c r="BE55" s="1"/>
-    </row>
-    <row r="56" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X55" s="1"/>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>12</v>
       </c>
@@ -4696,37 +4345,37 @@
       <c r="J56" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="AV56" s="8">
+      <c r="O56" s="8">
         <v>45245.549722222226</v>
       </c>
-      <c r="AW56" s="8">
+      <c r="P56" s="8">
         <v>45246.855300925927</v>
       </c>
-      <c r="AX56" s="1">
+      <c r="Q56" s="1">
         <f t="shared" si="1"/>
         <v>31.333888888824731</v>
       </c>
-      <c r="AY56" s="1">
+      <c r="R56" s="1">
         <v>10</v>
       </c>
-      <c r="AZ56" s="4">
+      <c r="S56" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA56" s="4">
+      <c r="T56" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB56" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC56" s="9">
+      <c r="U56" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V56" s="9">
         <v>382782</v>
       </c>
-      <c r="BD56" s="9">
+      <c r="W56" s="9">
         <v>9964814</v>
       </c>
-      <c r="BE56" s="1"/>
-    </row>
-    <row r="57" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X56" s="1"/>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>12</v>
       </c>
@@ -4757,37 +4406,37 @@
       <c r="J57" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="AV57" s="8">
+      <c r="O57" s="8">
         <v>45252.63181712963</v>
       </c>
-      <c r="AW57" s="8">
+      <c r="P57" s="8">
         <v>45253.958240740743</v>
       </c>
-      <c r="AX57" s="1">
+      <c r="Q57" s="1">
         <f t="shared" si="1"/>
         <v>31.83416666672565</v>
       </c>
-      <c r="AY57" s="1">
+      <c r="R57" s="1">
         <v>10</v>
       </c>
-      <c r="AZ57" s="4">
+      <c r="S57" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA57" s="4">
+      <c r="T57" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB57" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC57" s="9">
+      <c r="U57" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V57" s="9">
         <v>382782</v>
       </c>
-      <c r="BD57" s="9">
+      <c r="W57" s="9">
         <v>9964814</v>
       </c>
-      <c r="BE57" s="1"/>
-    </row>
-    <row r="58" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X57" s="1"/>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>12</v>
       </c>
@@ -4818,37 +4467,37 @@
       <c r="J58" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="AV58" s="8">
+      <c r="O58" s="8">
         <v>45257.562164351853</v>
       </c>
-      <c r="AW58" s="8">
+      <c r="P58" s="8">
         <v>45258.860810185186</v>
       </c>
-      <c r="AX58" s="1">
+      <c r="Q58" s="1">
         <f t="shared" si="1"/>
         <v>31.167499999981374</v>
       </c>
-      <c r="AY58" s="1">
+      <c r="R58" s="1">
         <v>10</v>
       </c>
-      <c r="AZ58" s="4">
+      <c r="S58" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA58" s="4">
+      <c r="T58" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB58" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC58" s="9">
+      <c r="U58" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V58" s="9">
         <v>382782</v>
       </c>
-      <c r="BD58" s="9">
+      <c r="W58" s="9">
         <v>9964814</v>
       </c>
-      <c r="BE58" s="1"/>
-    </row>
-    <row r="59" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X58" s="1"/>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>15</v>
       </c>
@@ -4880,46 +4529,39 @@
         <v>100</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="P59"/>
-      <c r="S59"/>
-      <c r="X59"/>
-      <c r="Y59"/>
-      <c r="Z59"/>
-      <c r="AA59"/>
-      <c r="AB59"/>
-      <c r="AV59" s="3">
+        <v>110</v>
+      </c>
+      <c r="O59" s="3">
         <v>45210.711157407408</v>
       </c>
-      <c r="AW59" s="3">
+      <c r="P59" s="3">
         <v>45212.113923611112</v>
       </c>
-      <c r="AX59" s="1">
+      <c r="Q59" s="1">
         <f t="shared" si="1"/>
         <v>33.666388888901565</v>
       </c>
-      <c r="AY59" s="1">
+      <c r="R59" s="1">
         <v>10</v>
       </c>
-      <c r="AZ59" s="4">
+      <c r="S59" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA59" s="4">
+      <c r="T59" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB59" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC59" s="9">
+      <c r="U59" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V59" s="9">
         <v>382134</v>
       </c>
-      <c r="BD59" s="9">
+      <c r="W59" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE59" s="1"/>
-    </row>
-    <row r="60" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X59" s="1"/>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>15</v>
       </c>
@@ -4951,48 +4593,41 @@
         <v>100</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="P60"/>
-      <c r="S60"/>
-      <c r="X60"/>
-      <c r="Y60"/>
-      <c r="Z60"/>
-      <c r="AA60"/>
-      <c r="AB60"/>
-      <c r="AV60" s="3">
+        <v>110</v>
+      </c>
+      <c r="O60" s="3">
         <v>45210.620173611111</v>
       </c>
-      <c r="AW60" s="3">
+      <c r="P60" s="3">
         <v>45211.946550925924</v>
       </c>
-      <c r="AX60" s="1">
+      <c r="Q60" s="1">
         <f t="shared" si="1"/>
         <v>31.833055555529427</v>
       </c>
-      <c r="AY60" s="1">
+      <c r="R60" s="1">
         <v>10</v>
       </c>
-      <c r="AZ60" s="4">
+      <c r="S60" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA60" s="4">
+      <c r="T60" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB60" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC60" s="9">
+      <c r="U60" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V60" s="9">
         <v>382134</v>
       </c>
-      <c r="BD60" s="9">
+      <c r="W60" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE60" s="1" t="s">
+      <c r="X60" s="1" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="61" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>15</v>
       </c>
@@ -5024,39 +4659,39 @@
         <v>100</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV61" s="3">
+        <v>110</v>
+      </c>
+      <c r="O61" s="3">
         <v>45217.512002314812</v>
       </c>
-      <c r="AW61" s="3">
+      <c r="P61" s="3">
         <v>45218.761979166666</v>
       </c>
-      <c r="AX61" s="1">
+      <c r="Q61" s="1">
         <f t="shared" si="1"/>
         <v>29.9994444444892</v>
       </c>
-      <c r="AY61" s="1">
+      <c r="R61" s="1">
         <v>10</v>
       </c>
-      <c r="AZ61" s="4">
+      <c r="S61" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA61" s="4">
+      <c r="T61" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB61" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC61" s="9">
+      <c r="U61" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V61" s="9">
         <v>382134</v>
       </c>
-      <c r="BD61" s="9">
+      <c r="W61" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE61" s="4"/>
-    </row>
-    <row r="62" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X61" s="4"/>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>15</v>
       </c>
@@ -5088,39 +4723,39 @@
         <v>100</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV62" s="3">
+        <v>110</v>
+      </c>
+      <c r="O62" s="3">
         <v>45217.512083333335</v>
       </c>
-      <c r="AW62" s="3">
+      <c r="P62" s="3">
         <v>45218.838449074072</v>
       </c>
-      <c r="AX62" s="1">
+      <c r="Q62" s="1">
         <f t="shared" si="1"/>
         <v>31.832777777686715</v>
       </c>
-      <c r="AY62" s="1">
+      <c r="R62" s="1">
         <v>10</v>
       </c>
-      <c r="AZ62" s="4">
+      <c r="S62" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA62" s="4">
+      <c r="T62" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB62" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC62" s="9">
+      <c r="U62" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V62" s="9">
         <v>382134</v>
       </c>
-      <c r="BD62" s="9">
+      <c r="W62" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE62" s="4"/>
-    </row>
-    <row r="63" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X62" s="4"/>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>15</v>
       </c>
@@ -5152,39 +4787,39 @@
         <v>100</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV63" s="8">
+        <v>110</v>
+      </c>
+      <c r="O63" s="8">
         <v>45224.556331018517</v>
       </c>
-      <c r="AW63" s="8">
+      <c r="P63" s="8">
         <v>45225.445208333331</v>
       </c>
-      <c r="AX63" s="1">
+      <c r="Q63" s="1">
         <f t="shared" si="1"/>
         <v>21.333055555529427</v>
       </c>
-      <c r="AY63" s="1">
+      <c r="R63" s="1">
         <v>10</v>
       </c>
-      <c r="AZ63" s="4">
+      <c r="S63" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA63" s="4">
+      <c r="T63" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB63" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC63" s="9">
+      <c r="U63" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V63" s="9">
         <v>382134</v>
       </c>
-      <c r="BD63" s="9">
+      <c r="W63" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE63" s="1"/>
-    </row>
-    <row r="64" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X63" s="1"/>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>15</v>
       </c>
@@ -5216,39 +4851,39 @@
         <v>100</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV64" s="8">
+        <v>110</v>
+      </c>
+      <c r="O64" s="8">
         <v>45224.562291666669</v>
       </c>
-      <c r="AW64" s="8">
+      <c r="P64" s="8">
         <v>45225.548414351855</v>
       </c>
-      <c r="AX64" s="1">
+      <c r="Q64" s="1">
         <f t="shared" si="1"/>
         <v>23.666944444470573</v>
       </c>
-      <c r="AY64" s="1">
+      <c r="R64" s="1">
         <v>10</v>
       </c>
-      <c r="AZ64" s="4">
+      <c r="S64" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA64" s="4">
+      <c r="T64" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB64" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC64" s="9">
+      <c r="U64" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V64" s="9">
         <v>382134</v>
       </c>
-      <c r="BD64" s="9">
+      <c r="W64" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE64" s="1"/>
-    </row>
-    <row r="65" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X64" s="1"/>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>15</v>
       </c>
@@ -5280,39 +4915,39 @@
         <v>100</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV65" s="8">
+        <v>110</v>
+      </c>
+      <c r="O65" s="8">
         <v>45231.528043981481</v>
       </c>
-      <c r="AW65" s="8">
+      <c r="P65" s="8">
         <v>45232.569699074076</v>
       </c>
-      <c r="AX65" s="1">
+      <c r="Q65" s="1">
         <f t="shared" si="1"/>
         <v>24.999722222273704</v>
       </c>
-      <c r="AY65" s="1">
+      <c r="R65" s="1">
         <v>10</v>
       </c>
-      <c r="AZ65" s="4">
+      <c r="S65" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA65" s="4">
+      <c r="T65" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB65" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC65" s="9">
+      <c r="U65" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V65" s="9">
         <v>382134</v>
       </c>
-      <c r="BD65" s="9">
+      <c r="W65" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE65" s="1"/>
-    </row>
-    <row r="66" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X65" s="1"/>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>15</v>
       </c>
@@ -5344,40 +4979,39 @@
         <v>100</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="S66"/>
-      <c r="AV66" s="8">
+        <v>110</v>
+      </c>
+      <c r="O66" s="8">
         <v>45231.529537037037</v>
       </c>
-      <c r="AW66" s="8">
+      <c r="P66" s="8">
         <v>45232.793437499997</v>
       </c>
-      <c r="AX66" s="1">
-        <f t="shared" ref="AX66:AX73" si="2">(AW66-AV66)*24</f>
+      <c r="Q66" s="1">
+        <f t="shared" ref="Q66:Q73" si="2">(P66-O66)*24</f>
         <v>30.333611111040227</v>
       </c>
-      <c r="AY66" s="1">
+      <c r="R66" s="1">
         <v>10</v>
       </c>
-      <c r="AZ66" s="4">
+      <c r="S66" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA66" s="4">
+      <c r="T66" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB66" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC66" s="9">
+      <c r="U66" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V66" s="9">
         <v>382134</v>
       </c>
-      <c r="BD66" s="9">
+      <c r="W66" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE66" s="1"/>
-    </row>
-    <row r="67" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X66" s="1"/>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>15</v>
       </c>
@@ -5409,39 +5043,39 @@
         <v>100</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV67" s="8">
+        <v>110</v>
+      </c>
+      <c r="O67" s="8">
         <v>45238.527962962966</v>
       </c>
-      <c r="AW67" s="8">
+      <c r="P67" s="8">
         <v>45239.833506944444</v>
       </c>
-      <c r="AX67" s="1">
+      <c r="Q67" s="1">
         <f t="shared" si="2"/>
         <v>31.333055555471219</v>
       </c>
-      <c r="AY67" s="1">
+      <c r="R67" s="1">
         <v>10</v>
       </c>
-      <c r="AZ67" s="4">
+      <c r="S67" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA67" s="4">
+      <c r="T67" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB67" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC67" s="9">
+      <c r="U67" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V67" s="9">
         <v>382134</v>
       </c>
-      <c r="BD67" s="9">
+      <c r="W67" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE67" s="1"/>
-    </row>
-    <row r="68" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X67" s="1"/>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>15</v>
       </c>
@@ -5473,39 +5107,39 @@
         <v>100</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV68" s="8">
+        <v>110</v>
+      </c>
+      <c r="O68" s="8">
         <v>45238.528333333335</v>
       </c>
-      <c r="AW68" s="8">
+      <c r="P68" s="8">
         <v>45240.097800925927</v>
       </c>
-      <c r="AX68" s="1">
+      <c r="Q68" s="1">
         <f t="shared" si="2"/>
         <v>37.66722222219687</v>
       </c>
-      <c r="AY68" s="1">
+      <c r="R68" s="1">
         <v>10</v>
       </c>
-      <c r="AZ68" s="4">
+      <c r="S68" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA68" s="4">
+      <c r="T68" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB68" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC68" s="9">
+      <c r="U68" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V68" s="9">
         <v>382134</v>
       </c>
-      <c r="BD68" s="9">
+      <c r="W68" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE68" s="1"/>
-    </row>
-    <row r="69" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X68" s="1"/>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>15</v>
       </c>
@@ -5537,41 +5171,41 @@
         <v>100</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV69" s="7">
+        <v>110</v>
+      </c>
+      <c r="O69" s="7">
         <v>45245.582766203705</v>
       </c>
-      <c r="AW69" s="7">
+      <c r="P69" s="7">
         <v>45246.742488425924</v>
       </c>
-      <c r="AX69" s="6">
+      <c r="Q69" s="6">
         <f t="shared" si="2"/>
         <v>27.833333333255723</v>
       </c>
-      <c r="AY69" s="6">
+      <c r="R69" s="6">
         <v>10</v>
       </c>
-      <c r="AZ69" s="4">
+      <c r="S69" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA69" s="4">
+      <c r="T69" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB69" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC69" s="9">
+      <c r="U69" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V69" s="9">
         <v>382134</v>
       </c>
-      <c r="BD69" s="9">
+      <c r="W69" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE69" s="1" t="s">
+      <c r="X69" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="70" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>15</v>
       </c>
@@ -5603,39 +5237,39 @@
         <v>100</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV70" s="8">
+        <v>110</v>
+      </c>
+      <c r="O70" s="8">
         <v>45245.582303240742</v>
       </c>
-      <c r="AW70" s="8">
+      <c r="P70" s="8">
         <v>45247.151770833334</v>
       </c>
-      <c r="AX70" s="1">
+      <c r="Q70" s="1">
         <f t="shared" si="2"/>
         <v>37.66722222219687</v>
       </c>
-      <c r="AY70" s="1">
+      <c r="R70" s="1">
         <v>10</v>
       </c>
-      <c r="AZ70" s="4">
+      <c r="S70" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA70" s="4">
+      <c r="T70" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB70" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC70" s="9">
+      <c r="U70" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V70" s="9">
         <v>382134</v>
       </c>
-      <c r="BD70" s="9">
+      <c r="W70" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE70" s="1"/>
-    </row>
-    <row r="71" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X70" s="1"/>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>15</v>
       </c>
@@ -5667,41 +5301,41 @@
         <v>100</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV71" s="7">
+        <v>110</v>
+      </c>
+      <c r="O71" s="7">
         <v>45252.680300925924</v>
       </c>
-      <c r="AW71" s="7">
+      <c r="P71" s="7">
         <v>45253.8747337963</v>
       </c>
-      <c r="AX71" s="6">
+      <c r="Q71" s="6">
         <f t="shared" si="2"/>
         <v>28.666388889017981</v>
       </c>
-      <c r="AY71" s="6">
+      <c r="R71" s="6">
         <v>10</v>
       </c>
-      <c r="AZ71" s="4">
+      <c r="S71" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA71" s="4">
+      <c r="T71" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB71" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC71" s="9">
+      <c r="U71" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V71" s="9">
         <v>382134</v>
       </c>
-      <c r="BD71" s="9">
+      <c r="W71" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE71" s="6" t="s">
+      <c r="X71" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:57" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>15</v>
       </c>
@@ -5733,39 +5367,39 @@
         <v>100</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV72" s="8">
+        <v>110</v>
+      </c>
+      <c r="O72" s="8">
         <v>45252.673402777778</v>
       </c>
-      <c r="AW72" s="8">
+      <c r="P72" s="8">
         <v>45253.985925925925</v>
       </c>
-      <c r="AX72" s="1">
+      <c r="Q72" s="1">
         <f t="shared" si="2"/>
         <v>31.5005555555108</v>
       </c>
-      <c r="AY72" s="1">
+      <c r="R72" s="1">
         <v>10</v>
       </c>
-      <c r="AZ72" s="4">
+      <c r="S72" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA72" s="4">
+      <c r="T72" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB72" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC72" s="9">
+      <c r="U72" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V72" s="9">
         <v>382134</v>
       </c>
-      <c r="BD72" s="9">
+      <c r="W72" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE72" s="1"/>
-    </row>
-    <row r="73" spans="1:57" x14ac:dyDescent="0.25">
+      <c r="X72" s="1"/>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>15</v>
       </c>
@@ -5797,42 +5431,43 @@
         <v>100</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="AV73" s="8">
+        <v>110</v>
+      </c>
+      <c r="O73" s="8">
         <v>45257.597372685188</v>
       </c>
-      <c r="AW73" s="8">
+      <c r="P73" s="8">
         <v>45258.798750000002</v>
       </c>
-      <c r="AX73" s="1">
+      <c r="Q73" s="1">
         <f t="shared" si="2"/>
         <v>28.833055555529427</v>
       </c>
-      <c r="AY73" s="1">
+      <c r="R73" s="1">
         <v>10</v>
       </c>
-      <c r="AZ73" s="4">
+      <c r="S73" s="4">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="BA73" s="4">
+      <c r="T73" s="4">
         <v>0.01</v>
       </c>
-      <c r="BB73" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="BC73" s="9">
+      <c r="U73" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="V73" s="9">
         <v>382134</v>
       </c>
-      <c r="BD73" s="9">
+      <c r="W73" s="9">
         <v>9964854</v>
       </c>
-      <c r="BE73" s="1"/>
+      <c r="X73" s="1"/>
     </row>
   </sheetData>
-  <sortState ref="A2:BE73">
+  <sortState ref="A2:X73">
     <sortCondition ref="B1:B73"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>